--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_新しい推計の入力値_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_新しい推計の入力値_20260925.xlsx
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>6,095</t>
+          <t>6,048</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">

--- a/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_新しい推計の入力値_20260925.xlsx
+++ b/小野町_引継ぎ_整理済/11_見える化出力依頼/小野町_見える化_新しい推計の入力値_20260925.xlsx
@@ -972,7 +972,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>町との協議が要ります。当面は0で構いません。年報 様式4 の保有額は12,000千円ですが、令和4年度末の120,000千円から1桁減っており、基金運用状況調書での確認をお願いしています</t>
+          <t>町との協議が要ります。当面は0で構いません。残高は令和5年度末120,000千円（町の財務書類）、令和8年度末見込210,000千円です。令和7年度末の残高（財産に関する調書）の確認をお願いしています</t>
         </is>
       </c>
     </row>
